--- a/AUiX_Expertise_Map_Data.xlsx
+++ b/AUiX_Expertise_Map_Data.xlsx
@@ -1206,7 +1206,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Treholm</t>
+          <t>Trenholm</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Treholm</t>
+          <t>Trenholm</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Treholm</t>
+          <t>Trenholm</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Treholm</t>
+          <t>Trenholm</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
